--- a/backend/test/probka.xlsx
+++ b/backend/test/probka.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\svn.czelen.dyndns.org\projekty\mailing\backend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F39248E-2830-4320-980B-4B1055DF4D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECCB846-A461-48B1-9E95-5FF2468F5C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{904A970D-EB77-4F2E-9964-290B7FB539D1}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
-  <si>
-    <t>Address</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>miasto</t>
   </si>
@@ -40,45 +37,30 @@
     <t>Szkola Podstawowa</t>
   </si>
   <si>
-    <t>02700047@pro.onet.pl</t>
-  </si>
-  <si>
     <t>PRZEWORSK</t>
   </si>
   <si>
     <t>PUBLICZNE GIMNAZJUM</t>
   </si>
   <si>
-    <t>05252s@gazeta.pl</t>
-  </si>
-  <si>
     <t>DĄBRÓWKA K. RADZYMINA</t>
   </si>
   <si>
     <t>PUBLICZNA szkola podstawowa IM. ADELI GOSZCZYŃSKIEJ WE WSZEBORACH</t>
   </si>
   <si>
-    <t>0984@interia.pl</t>
-  </si>
-  <si>
     <t>JÓZEFÓW</t>
   </si>
   <si>
     <t>SZKOlA PODSTAWOWA IM. KONRADA BARTOSZEWSKIEGO-WIRA</t>
   </si>
   <si>
-    <t>10teresa@wp.pl</t>
-  </si>
-  <si>
     <t>KRAKÓW</t>
   </si>
   <si>
     <t>GIMNAZJUM NR 46 SPORTOWE</t>
   </si>
   <si>
-    <t>12287961@pro.onet.pl</t>
-  </si>
-  <si>
     <t>Gimnazjum</t>
   </si>
   <si>
@@ -88,125 +70,92 @@
     <t>Liceum</t>
   </si>
   <si>
-    <t>160sp@wp.pl</t>
-  </si>
-  <si>
     <t>Łódź-Polesie - delegatura</t>
   </si>
   <si>
     <t>szkola podstawowa NR 160 IM. POWSTAŃCÓW ŚLĄSKICH</t>
   </si>
   <si>
-    <t>1danazab@wp.pl</t>
-  </si>
-  <si>
     <t>Podwiesk</t>
   </si>
   <si>
     <t>Publiczne Gimnazjum im. Ziemi Chelmilskiej w Podwiesku</t>
   </si>
   <si>
-    <t>1gim@wp.pl</t>
-  </si>
-  <si>
     <t>TRZEBINIA</t>
   </si>
   <si>
     <t>GIMNAZJUM NR 1 IM. MIKOlAJA KOPERNIKA</t>
   </si>
   <si>
-    <t>1gimslupia@interia.pl</t>
-  </si>
-  <si>
     <t>SŁUPIA</t>
   </si>
   <si>
     <t>I PUBLICZNE GIMNAZJUM</t>
   </si>
   <si>
-    <t>1spstanislawdolny@vp.pl</t>
-  </si>
-  <si>
     <t>Kalwaria Zebrzydowska - obszar wiejski</t>
   </si>
   <si>
     <t>szkola podstawowa NR 1 IM. JANA PAWŁA II W STANISŁAWIU DOLNYM</t>
   </si>
   <si>
-    <t>206@o2.pl</t>
-  </si>
-  <si>
     <t>Łódź-Bałuty - delegatura</t>
   </si>
   <si>
     <t>szkola podstawowa NR 206</t>
   </si>
   <si>
-    <t>20980838@pro.onet.pl</t>
-  </si>
-  <si>
     <t>SZAFLARY</t>
   </si>
   <si>
     <t>GIMNAZJUM</t>
   </si>
   <si>
-    <t>22662446@pro.onet.pl</t>
-  </si>
-  <si>
     <t>Szaflary</t>
   </si>
   <si>
-    <t>271161@interia.pl</t>
-  </si>
-  <si>
     <t>RUDA ŚLĄSKA</t>
   </si>
   <si>
     <t>SZKOlA PODSTAWOWA NR 6</t>
   </si>
   <si>
-    <t>2gimnazjumwyszkow1@wp.pl</t>
-  </si>
-  <si>
     <t>WYSZKÓW</t>
   </si>
   <si>
     <t>Gimnazjum Nr 2 w Wyszkowie</t>
   </si>
   <si>
-    <t>2gim_laskarzew@wp.pl</t>
-  </si>
-  <si>
     <t>Łaskarzew</t>
   </si>
   <si>
     <t>Zasadnicza Szkola Zawodowa w laskarzewie</t>
   </si>
   <si>
-    <t>2grace@interia.pl</t>
-  </si>
-  <si>
     <t>Kluczbork</t>
   </si>
   <si>
     <t>Zespol Szkol Ponadgimnazjalnych Nr 1</t>
   </si>
   <si>
-    <t>2loinowroclaw@poczta.internetdsl.pl</t>
-  </si>
-  <si>
     <t>Inowrocław</t>
   </si>
   <si>
     <t>II Liceum im. M. Konopnickiej</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>marek-czelen@wp.pl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -357,6 +306,14 @@
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="33">
@@ -656,7 +613,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -699,11 +656,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% — akcent 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% — akcent 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% — akcent 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -731,6 +690,7 @@
     <cellStyle name="Dane wejściowe" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Dane wyjściowe" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Dobry" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Hiperłącze" xfId="42" builtinId="8"/>
     <cellStyle name="Komórka połączona" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Komórka zaznaczona" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Nagłówek 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1059,274 +1019,281 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199533F4-5360-4886-8C81-B89474075CF5}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="48.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="D18" t="s">
         <v>38</v>
       </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
         <v>40</v>
       </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{FE132DB1-77C7-4499-87EB-5EB08A9F0A3B}"/>
+    <hyperlink ref="A3:A19" r:id="rId2" display="marek-czelen@wp.pl" xr:uid="{4D6146B7-C76F-4873-859B-E2AFC2605F43}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/test/probka.xlsx
+++ b/backend/test/probka.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\svn.czelen.dyndns.org\projekty\mailing\backend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECCB846-A461-48B1-9E95-5FF2468F5C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B337D20-51DB-43A8-9FB7-41F8B2DC4451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{904A970D-EB77-4F2E-9964-290B7FB539D1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>miasto</t>
   </si>
@@ -34,9 +34,6 @@
     <t>szkola podstawowa</t>
   </si>
   <si>
-    <t>Szkola Podstawowa</t>
-  </si>
-  <si>
     <t>PRZEWORSK</t>
   </si>
   <si>
@@ -55,100 +52,16 @@
     <t>SZKOlA PODSTAWOWA IM. KONRADA BARTOSZEWSKIEGO-WIRA</t>
   </si>
   <si>
-    <t>KRAKÓW</t>
-  </si>
-  <si>
-    <t>GIMNAZJUM NR 46 SPORTOWE</t>
-  </si>
-  <si>
-    <t>Gimnazjum</t>
-  </si>
-  <si>
-    <t>GIMNAZJUM NR 25</t>
-  </si>
-  <si>
-    <t>Liceum</t>
-  </si>
-  <si>
-    <t>Łódź-Polesie - delegatura</t>
-  </si>
-  <si>
-    <t>szkola podstawowa NR 160 IM. POWSTAŃCÓW ŚLĄSKICH</t>
-  </si>
-  <si>
-    <t>Podwiesk</t>
-  </si>
-  <si>
-    <t>Publiczne Gimnazjum im. Ziemi Chelmilskiej w Podwiesku</t>
-  </si>
-  <si>
-    <t>TRZEBINIA</t>
-  </si>
-  <si>
-    <t>GIMNAZJUM NR 1 IM. MIKOlAJA KOPERNIKA</t>
-  </si>
-  <si>
-    <t>SŁUPIA</t>
-  </si>
-  <si>
-    <t>I PUBLICZNE GIMNAZJUM</t>
-  </si>
-  <si>
-    <t>Kalwaria Zebrzydowska - obszar wiejski</t>
-  </si>
-  <si>
-    <t>szkola podstawowa NR 1 IM. JANA PAWŁA II W STANISŁAWIU DOLNYM</t>
-  </si>
-  <si>
-    <t>Łódź-Bałuty - delegatura</t>
-  </si>
-  <si>
-    <t>szkola podstawowa NR 206</t>
-  </si>
-  <si>
-    <t>SZAFLARY</t>
-  </si>
-  <si>
-    <t>GIMNAZJUM</t>
-  </si>
-  <si>
-    <t>Szaflary</t>
-  </si>
-  <si>
-    <t>RUDA ŚLĄSKA</t>
-  </si>
-  <si>
-    <t>SZKOlA PODSTAWOWA NR 6</t>
-  </si>
-  <si>
-    <t>WYSZKÓW</t>
-  </si>
-  <si>
-    <t>Gimnazjum Nr 2 w Wyszkowie</t>
-  </si>
-  <si>
-    <t>Łaskarzew</t>
-  </si>
-  <si>
-    <t>Zasadnicza Szkola Zawodowa w laskarzewie</t>
-  </si>
-  <si>
-    <t>Kluczbork</t>
-  </si>
-  <si>
-    <t>Zespol Szkol Ponadgimnazjalnych Nr 1</t>
-  </si>
-  <si>
-    <t>Inowrocław</t>
-  </si>
-  <si>
-    <t>II Liceum im. M. Konopnickiej</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
     <t>marek-czelen@wp.pl</t>
+  </si>
+  <si>
+    <t>czelen@verx.pl</t>
+  </si>
+  <si>
+    <t>czelen.mc@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +938,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1039,260 +952,97 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
+      <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
+      <c r="A11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" t="s">
-        <v>4</v>
-      </c>
+      <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
+      <c r="A15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
-      </c>
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{FE132DB1-77C7-4499-87EB-5EB08A9F0A3B}"/>
     <hyperlink ref="A3:A19" r:id="rId2" display="marek-czelen@wp.pl" xr:uid="{4D6146B7-C76F-4873-859B-E2AFC2605F43}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{5C183346-0726-49B8-BA1B-BA34F7E0A92B}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{96F606A9-071C-4D2B-A24A-B9551BA78E44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
